--- a/ksoft/docs/fields_details/jalmeida/IN0518.xlsx
+++ b/ksoft/docs/fields_details/jalmeida/IN0518.xlsx
@@ -2103,13 +2103,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E609AF9-9AB3-408D-A6C8-657F4D14F073}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8853C2F4-7803-4142-8DEA-510DF92EFF3E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FB0E2FC-223B-4733-9AF5-2355A1BD6773}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{237B32EC-7EA7-4C0D-8E6E-A089984C56A5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F1A8A45-6BF6-4616-A6AA-C2B3CB35C0BC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAE339DA-459E-4A80-A980-7EE794D3C39C}"/>
 </file>
--- a/ksoft/docs/fields_details/jalmeida/IN0518.xlsx
+++ b/ksoft/docs/fields_details/jalmeida/IN0518.xlsx
@@ -2103,13 +2103,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8853C2F4-7803-4142-8DEA-510DF92EFF3E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E609AF9-9AB3-408D-A6C8-657F4D14F073}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{237B32EC-7EA7-4C0D-8E6E-A089984C56A5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FB0E2FC-223B-4733-9AF5-2355A1BD6773}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAE339DA-459E-4A80-A980-7EE794D3C39C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F1A8A45-6BF6-4616-A6AA-C2B3CB35C0BC}"/>
 </file>